--- a/E-mailsRCs.xlsx
+++ b/E-mailsRCs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="8_{FD5BF093-0F41-4213-9857-AE6C12553210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF127FE3-1BF6-4FF1-A610-F9B6277AB49E}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="8_{FD5BF093-0F41-4213-9857-AE6C12553210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED020219-3C09-4B1C-BEAF-F9A6AF3F63C2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{455581AF-9035-45DD-A77C-5681DBCBB5BA}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="220">
   <si>
     <t>RC</t>
   </si>
@@ -702,9 +702,6 @@
   </si>
   <si>
     <t>Email3</t>
-  </si>
-  <si>
-    <t>hellenbianchini19@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -2964,7 +2961,7 @@
         <v>118</v>
       </c>
       <c r="B224" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
